--- a/verification_forms/045_passport_verification_form--verification_forms.xlsx
+++ b/verification_forms/045_passport_verification_form--verification_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>passport_number</t>
+          <t>passport_number_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Passport Number</t>
+          <t>Passport Number 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>client_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>Client 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>photo_front</t>
+          <t>photo_front_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Photo Front</t>
+          <t>Photo Front 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>photo_back</t>
+          <t>photo_back_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Photo Back</t>
+          <t>Photo Back 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>date_of_issue</t>
+          <t>date_of_issue_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Date of Issue</t>
+          <t>Date Of Issue 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,9 +1101,9 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'john_smith'}</t>
+          <t>john_smith</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'John Smith'}</t>
+          <t>John Smith</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1165,63 +1165,63 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'bob_johnson'}</t>
+          <t>bob_johnson</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Bob Johnson'}</t>
+          <t>Bob Johnson</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>client_choices</t>
+          <t>client_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'john_smith'}</t>
+          <t>john_smith</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'John Smith'}</t>
+          <t>John Smith</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>client_choices</t>
+          <t>client_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>client_choices</t>
+          <t>client_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'bob_johnson'}</t>
+          <t>bob_johnson</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Bob Johnson'}</t>
+          <t>Bob Johnson</t>
         </is>
       </c>
     </row>
